--- a/PBG_Mendoza_1970-2022_ordenado.xlsx
+++ b/PBG_Mendoza_1970-2022_ordenado.xlsx
@@ -5,25 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Facultad\Proyecto-evolucion-salarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0AF6E04-36C6-40BF-8196-9932583BFF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95B218E-9BA0-4EAA-B509-1EFB85E5B91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas" sheetId="1" r:id="rId1"/>
     <sheet name="PBG por tramo" sheetId="2" r:id="rId2"/>
-    <sheet name="PBG nominal 2004-2022" sheetId="3" r:id="rId3"/>
-    <sheet name="IPC INDEC" sheetId="4" r:id="rId4"/>
-    <sheet name="Coeficiente de empalme (B-C)" sheetId="5" r:id="rId5"/>
-    <sheet name="PBG índice 1970-1985" sheetId="6" r:id="rId6"/>
-    <sheet name="PBI Ferreres (nacional)" sheetId="7" r:id="rId7"/>
-    <sheet name="Coeficiente de empalme (A-B)" sheetId="8" r:id="rId8"/>
-    <sheet name="PBG a precios de 1999" sheetId="9" r:id="rId9"/>
+    <sheet name="IPC INDEC" sheetId="4" r:id="rId3"/>
+    <sheet name="Coeficiente de empalme (B-C)" sheetId="5" r:id="rId4"/>
+    <sheet name="PBI Ferreres (nacional)" sheetId="7" r:id="rId5"/>
+    <sheet name="Coeficiente de empalme (A-B)" sheetId="8" r:id="rId6"/>
+    <sheet name="PBG a precios de 1999" sheetId="9" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="63">
   <si>
     <t>Producto Bruto Geográfico de Mendoza, 1970-2022</t>
   </si>
@@ -71,9 +69,6 @@
     <t xml:space="preserve">  2004-2022</t>
   </si>
   <si>
-    <t>En miles de pesos de 1993 (también existe una versión a precios corrientes, hoja aparte).</t>
-  </si>
-  <si>
     <t>Empalme B-&gt;C</t>
   </si>
   <si>
@@ -83,9 +78,6 @@
     <t>Empalme A-&gt;B</t>
   </si>
   <si>
-    <t>No hay año de solapamiento entre 1970-1985 y 1986-1993. Se probó primero la tabla oficial de conversión monetaria (Austral-&gt;Peso) + IPC, y dio un salto de nivel de ~30.000 veces frente al tramo siguiente — señal de que el cambio de año base implica un recálculo metodológico, no solo cambio de moneda y precios. Se resolvió usando el PBI nacional (Ferreres, hoja 'PBI Ferreres (nacional)') como proxy del crecimiento real de Mendoza en 1986, para despejar el coeficiente de empalme implícito (ver hoja 'Coeficiente de empalme (A-B)'). Ese coeficiente combina moneda + metodología: no aísla el tipo de cambio Austral-Peso por sí solo.</t>
-  </si>
-  <si>
     <t>Base 1999</t>
   </si>
   <si>
@@ -95,9 +87,6 @@
     <t>Quiebre 2003-2004</t>
   </si>
   <si>
-    <t>La DEIE documenta que no hay empalme formal entre las mediciones 1991-2003 y 2004-2022 (cambio metodológico). Se dejaron como continuas por ser la única fuente disponible; el salto de +16,4% en 2004 refleja ese quiebre, no un error.</t>
-  </si>
-  <si>
     <t>Hoja 'PBG índice 1970-1985'</t>
   </si>
   <si>
@@ -107,9 +96,6 @@
     <t>Producto Bruto Geográfico de Mendoza — series por tramo de publicación</t>
   </si>
   <si>
-    <t>Fuente: DEIE Mendoza. Cada tramo está a precios constantes del año base indicado (ver hoja Notas).</t>
-  </si>
-  <si>
     <t>Año</t>
   </si>
   <si>
@@ -149,15 +135,6 @@
     <t>2004-2022</t>
   </si>
   <si>
-    <t>PBG Mendoza a precios corrientes, 2004-2022</t>
-  </si>
-  <si>
-    <t>Fuente: DEIE Mendoza. Valores nominales (sin ajustar por inflación).</t>
-  </si>
-  <si>
-    <t>PBG (miles $ corrientes)</t>
-  </si>
-  <si>
     <t>IPC INDEC — Nivel general, base 1999=100</t>
   </si>
   <si>
@@ -185,33 +162,15 @@
     <t>El tramo 1970-1985 NO se empalma con este: no hay año de solapamiento con 1986-1993, y se comprobó que usar la tabla de conversión monetaria (Austral-&gt;Peso) junto con el IPC da un salto de nivel de ~30.000 veces, incompatible con la evolución real observada. Ver hoja 'PBG índice 1970-1985'.</t>
   </si>
   <si>
-    <t>PBG Mendoza, 1970-1985 — índice propio (1970=100)</t>
-  </si>
-  <si>
-    <t>NO comparable en nivel con el tramo 1986-2022 (distinto año base, sin año de solapamiento).</t>
-  </si>
-  <si>
-    <t>PBG (Australes de 1970)</t>
-  </si>
-  <si>
-    <t>Índice (1970=100)</t>
-  </si>
-  <si>
     <t>PBI nacional a precios de mercado — Base Ferreres (mill. de $ de 1993)</t>
   </si>
   <si>
-    <t>Fuente: aportado por el usuario. Se usa como proxy de crecimiento real para el empalme 1985-1986 (sin año de solapamiento en el PBG de Mendoza).</t>
-  </si>
-  <si>
     <t>PBI (mill. $ de 1993)</t>
   </si>
   <si>
     <t>Coeficiente de empalme 1970-1985 -&gt; 1986-1993</t>
   </si>
   <si>
-    <t>Sin año de solapamiento entre tramos. Se usa el crecimiento real del PBI nacional (Ferreres) de 1986 como proxy del crecimiento real de Mendoza ese año, para despejar el coeficiente que hace empalmar los dos tramos.</t>
-  </si>
-  <si>
     <t>g_1986 (crecimiento real, proxy PBI nacional)</t>
   </si>
   <si>
@@ -224,9 +183,6 @@
     <t>PBG Mendoza, 1970-2022 — serie única, a precios constantes de 1999</t>
   </si>
   <si>
-    <t>1970-1985 empalmado con el PBI nacional (Ferreres) como proxy de crecimiento real en 1986 (sin año de solapamiento). 1986-2022 empalmado con años de solapamiento reales (1991-1993).</t>
-  </si>
-  <si>
     <t>Tramo de origen</t>
   </si>
   <si>
@@ -243,6 +199,27 @@
   </si>
   <si>
     <t>D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En miles de pesos de 1993 </t>
+  </si>
+  <si>
+    <t>No hay año de solapamiento entre 1970-1985 y 1986-1993. Se probó primero la tabla oficial de conversión monetaria (Austral-&gt;Peso) + IPC, y dio un salto de nivel de aprox 30.000 veces frente al tramo siguiente, osea que el cambio de año base implica un recálculo metodológico, no solo cambio de moneda y precios. Se resolvió usando el PBI nacional (Ferreres) como proxy del crecimiento real de Mendoza en 1986, para despejar el coeficiente de empalme implícito (ver hoja 'Coeficiente de empalme (A-B)'). Ese coeficiente combina moneda + metodología: no aísla el tipo de cambio Austral-Peso por sí solo.</t>
+  </si>
+  <si>
+    <t>Según La DEIE, no hay registro del empalme formal entre las mediciones 1991-2003 y 2004-2022, que hubo un cambio metodológico en la forma de medir el pbg. Se dejaron como continuas por ser la única fuente disponible; el salto de +16,4% en 2004 refleja esto mismo, no un error.</t>
+  </si>
+  <si>
+    <t>1970-1985 empalmado con el PBI nacional (Ferreres) como fuente de crecimiento real en 1986 (sin año de solapamiento). 1986-2022 empalmado con años de solapamiento reales (1991-1993).</t>
+  </si>
+  <si>
+    <t>Sin año de solapamiento entre tramos. Se usa el crecimiento real del PBI nacional (Ferreres) de 1986 como fuente del crecimiento real de Mendoza ese año, para despejar el coeficiente que hace empalmar los dos tramos.</t>
+  </si>
+  <si>
+    <t>Fuente: Ferreres. Se usa como fuente de crecimiento real para el empalme 1985-1986 (sin año de solapamiento en el PBG de Mendoza).</t>
+  </si>
+  <si>
+    <t>Fuente: DEIE Mendoza y P. Olguín. Cada tramo está a precios constantes del año base indicado (ver hoja Notas).</t>
   </si>
 </sst>
 </file>
@@ -443,12 +420,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -497,46 +469,16 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF003366"/>
-          <bgColor rgb="FF1B2A4A"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -684,13 +626,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -703,6 +638,48 @@
         <bottom style="thin">
           <color rgb="FFCCCCCC"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF003366"/>
+          <bgColor rgb="FF1B2A4A"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -2388,15 +2365,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{741094FC-1EF8-4ACF-AD2A-75769E382932}" name="Tabla1" displayName="Tabla1" ref="A4:D57" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{741094FC-1EF8-4ACF-AD2A-75769E382932}" name="Tabla1" displayName="Tabla1" ref="A4:D57" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="A4:D57" xr:uid="{741094FC-1EF8-4ACF-AD2A-75769E382932}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A00E71CC-573E-4A5D-884A-71559B0D0878}" name="Año" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{365C3385-0229-438C-B36E-9788B3607800}" name="Tramo de origen" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{19FBF4BE-C44D-4711-A3AB-20102B1B4CCB}" name="PBG (miles $ ctes. de 1999)" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{A00E71CC-573E-4A5D-884A-71559B0D0878}" name="Año" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{365C3385-0229-438C-B36E-9788B3607800}" name="Tramo de origen" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{19FBF4BE-C44D-4711-A3AB-20102B1B4CCB}" name="PBG (miles $ ctes. de 1999)" dataDxfId="1">
       <calculatedColumnFormula>'PBG por tramo'!E11*'Coeficiente de empalme (B-C)'!$B$8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9892B746-E94B-4597-8310-A0CF79184942}" name="Variación anual (%)" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{9892B746-E94B-4597-8310-A0CF79184942}" name="Variación anual (%)" dataDxfId="0">
       <calculatedColumnFormula>C5/C4-1</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2591,97 +2568,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="21"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="5" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2706,1205 +2683,1205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="F4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>1970</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="D5" s="4">
         <v>1970</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="E5" s="5">
+        <v>313.43</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>1971</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="4">
         <v>1970</v>
       </c>
-      <c r="E5" s="8">
-        <v>313.43</v>
-      </c>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>1971</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1970</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="E6" s="5">
         <v>334.41</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="6">
         <f t="shared" ref="F6:F20" si="0">E6/E5-1</f>
         <v>6.6936796094821949E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="4">
         <v>1972</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4">
         <v>1970</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="5">
         <v>356.26</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <f t="shared" si="0"/>
         <v>6.5338955174785385E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="4">
         <v>1973</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="4">
         <v>1970</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="5">
         <v>364.33</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="6">
         <f t="shared" si="0"/>
         <v>2.2651995733453001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="4">
         <v>1974</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="B9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4">
         <v>1970</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="5">
         <v>406.37</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="6">
         <f t="shared" si="0"/>
         <v>0.11538989377761921</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="4">
         <v>1975</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="4">
         <v>1970</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="5">
         <v>355.2</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="6">
         <f t="shared" si="0"/>
         <v>-0.12591972832640208</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="4">
         <v>1976</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="B11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="4">
         <v>1970</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="5">
         <v>404.05</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="6">
         <f t="shared" si="0"/>
         <v>0.13752815315315314</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="4">
         <v>1977</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="B12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="4">
         <v>1970</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="5">
         <v>380.63</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="6">
         <f t="shared" si="0"/>
         <v>-5.7963123375819881E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="4">
         <v>1978</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="B13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="4">
         <v>1970</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="5">
         <v>423.6</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="6">
         <f t="shared" si="0"/>
         <v>0.11289178467277949</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="4">
         <v>1979</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="B14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="4">
         <v>1970</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="5">
         <v>481.05</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="6">
         <f t="shared" si="0"/>
         <v>0.13562322946175631</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="4">
         <v>1980</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="B15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="4">
         <v>1970</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="5">
         <v>429.24</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="6">
         <f t="shared" si="0"/>
         <v>-0.10770190208917996</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="4">
         <v>1981</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="B16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="4">
         <v>1970</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="5">
         <v>351.83</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="6">
         <f t="shared" si="0"/>
         <v>-0.18034199981362409</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="4">
         <v>1982</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="7">
+      <c r="B17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="4">
         <v>1970</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="5">
         <v>360.43</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="6">
         <f t="shared" si="0"/>
         <v>2.4443623340818066E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="4">
         <v>1983</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="7">
+      <c r="B18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="4">
         <v>1970</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="5">
         <v>419.26</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="6">
         <f t="shared" si="0"/>
         <v>0.16322170740504394</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="4">
         <v>1984</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="B19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="4">
         <v>1970</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="5">
         <v>404.44</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="6">
         <f t="shared" si="0"/>
         <v>-3.5347994084816037E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="4">
         <v>1985</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="7">
+      <c r="B20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="4">
         <v>1970</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="5">
         <v>384.61</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="6">
         <f t="shared" si="0"/>
         <v>-4.9030758579764577E-2</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="4">
         <v>1986</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="7">
+      <c r="B22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="4">
         <v>1996</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="5">
         <v>267608.7</v>
       </c>
-      <c r="F22" s="7"/>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="4">
         <v>1987</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="7">
+      <c r="B23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="4">
         <v>1996</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="5">
         <v>271052</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="6">
         <f t="shared" ref="F23:F29" si="1">E23/E22-1</f>
         <v>1.2866920993226172E-2</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="4">
         <v>1988</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="B24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="4">
         <v>1996</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="5">
         <v>264473</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="6">
         <f t="shared" si="1"/>
         <v>-2.4272095391290271E-2</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="4">
         <v>1989</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="7">
+      <c r="B25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="4">
         <v>1996</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="5">
         <v>253410</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="6">
         <f t="shared" si="1"/>
         <v>-4.1830356974057792E-2</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="4">
         <v>1990</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="7">
+      <c r="B26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="4">
         <v>1996</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="5">
         <v>253627</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="6">
         <f t="shared" si="1"/>
         <v>8.5631979795586233E-4</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="4">
         <v>1991</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="7">
+      <c r="B27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="4">
         <v>1996</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="5">
         <v>259579</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="6">
         <f t="shared" si="1"/>
         <v>2.3467533030789411E-2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="4">
         <v>1992</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="B28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="4">
         <v>1996</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="5">
         <v>277469</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="6">
         <f t="shared" si="1"/>
         <v>6.891928854029028E-2</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="4">
         <v>1993</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="7">
+      <c r="B29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="4">
         <v>1996</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="5">
         <v>296965</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="6">
         <f t="shared" si="1"/>
         <v>7.0263705134627763E-2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="4">
         <v>1991</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="7">
+      <c r="B31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="4">
         <v>1993</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="5">
         <v>6485506.9469233304</v>
       </c>
-      <c r="F31" s="7"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32" s="4">
         <v>1992</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="7">
+      <c r="B32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="4">
         <v>1993</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="5">
         <v>7035025.5867938399</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="6">
         <f t="shared" ref="F32:F43" si="2">E32/E31-1</f>
         <v>8.4730252294494379E-2</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33" s="4">
         <v>1993</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="7">
+      <c r="B33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="4">
         <v>1993</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="5">
         <v>7761508.2247008998</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="6">
         <f t="shared" si="2"/>
         <v>0.10326652390160662</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34" s="4">
         <v>1994</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="7">
+      <c r="B34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="4">
         <v>1993</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="5">
         <v>8098028.3105721101</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="6">
         <f t="shared" si="2"/>
         <v>4.3357563520997067E-2</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
+      <c r="A35" s="4">
         <v>1995</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="7">
+      <c r="B35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="4">
         <v>1993</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="5">
         <v>7908811.3856461896</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="6">
         <f t="shared" si="2"/>
         <v>-2.3365801855606549E-2</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
+      <c r="A36" s="4">
         <v>1996</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36" s="7">
+      <c r="B36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="4">
         <v>1993</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="5">
         <v>8135361.8772270596</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="6">
         <f t="shared" si="2"/>
         <v>2.8645327411909172E-2</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
+      <c r="A37" s="4">
         <v>1997</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="7">
+      <c r="B37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="4">
         <v>1993</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="5">
         <v>8905959.4449048098</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="6">
         <f t="shared" si="2"/>
         <v>9.4721977867370466E-2</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
+      <c r="A38" s="4">
         <v>1998</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38" s="7">
+      <c r="B38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="4">
         <v>1993</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="5">
         <v>9488295.9322833791</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="6">
         <f t="shared" si="2"/>
         <v>6.5387282637103139E-2</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
+      <c r="A39" s="4">
         <v>1999</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D39" s="7">
+      <c r="B39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="4">
         <v>1993</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="5">
         <v>9252615.1693661101</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="6">
         <f t="shared" si="2"/>
         <v>-2.483910331204775E-2</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40" s="4">
         <v>2000</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40" s="7">
+      <c r="B40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="4">
         <v>1993</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="5">
         <v>9002038.4513383098</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="6">
         <f t="shared" si="2"/>
         <v>-2.7081718351090522E-2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
+      <c r="A41" s="4">
         <v>2001</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="7">
+      <c r="B41" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="4">
         <v>1993</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="5">
         <v>8322993.4966704398</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="6">
         <f t="shared" si="2"/>
         <v>-7.5432354387124145E-2</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
+      <c r="A42" s="4">
         <v>2002</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D42" s="7">
+      <c r="B42" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="4">
         <v>1993</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="5">
         <v>7772198.03942711</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="6">
         <f t="shared" si="2"/>
         <v>-6.6177566696846712E-2</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
+      <c r="A43" s="4">
         <v>2003</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D43" s="7">
+      <c r="B43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="4">
         <v>1993</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="5">
         <v>9339929.5945354104</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="6">
         <f t="shared" si="2"/>
         <v>0.20171019152567271</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
+      <c r="A45" s="4">
         <v>2004</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D45" s="7">
+      <c r="B45" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="4">
         <v>1993</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="5">
         <v>10874929.0970839</v>
       </c>
-      <c r="F45" s="7"/>
+      <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
+      <c r="A46" s="4">
         <v>2005</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46" s="7">
+      <c r="B46" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="4">
         <v>1993</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="5">
         <v>11380763.411127999</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="6">
         <f t="shared" ref="F46:F63" si="3">E46/E45-1</f>
         <v>4.6513803403071208E-2</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
+      <c r="A47" s="4">
         <v>2006</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="B47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="4">
         <v>1993</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="5">
         <v>12259303.9769339</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="6">
         <f t="shared" si="3"/>
         <v>7.7195222681360143E-2</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
+      <c r="A48" s="4">
         <v>2007</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" s="7">
+      <c r="B48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="4">
         <v>1993</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="5">
         <v>12770718.617713301</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="6">
         <f t="shared" si="3"/>
         <v>4.1716449950309986E-2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
+      <c r="A49" s="4">
         <v>2008</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49" s="7">
+      <c r="B49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" s="4">
         <v>1993</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="5">
         <v>13065173.973136401</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="6">
         <f t="shared" si="3"/>
         <v>2.3057070180426908E-2</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
+      <c r="A50" s="4">
         <v>2009</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D50" s="7">
+      <c r="B50" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="4">
         <v>1993</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="5">
         <v>12700761.7198551</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="6">
         <f t="shared" si="3"/>
         <v>-2.7891879130777508E-2</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
+      <c r="A51" s="4">
         <v>2010</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" s="7">
+      <c r="B51" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="4">
         <v>1993</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="5">
         <v>13262431.7233532</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="6">
         <f t="shared" si="3"/>
         <v>4.4223332102990343E-2</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
+      <c r="A52" s="4">
         <v>2011</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D52" s="7">
+      <c r="B52" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="4">
         <v>1993</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="5">
         <v>13739583.7038198</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="6">
         <f t="shared" si="3"/>
         <v>3.5977714375441838E-2</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
+      <c r="A53" s="4">
         <v>2012</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D53" s="7">
+      <c r="B53" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="4">
         <v>1993</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="5">
         <v>13545085.6393847</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="6">
         <f t="shared" si="3"/>
         <v>-1.4156037666630872E-2</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
+      <c r="A54" s="4">
         <v>2013</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D54" s="7">
+      <c r="B54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="4">
         <v>1993</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="5">
         <v>14211513.620518301</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="6">
         <f t="shared" si="3"/>
         <v>4.9200721123227487E-2</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
+      <c r="A55" s="4">
         <v>2014</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D55" s="7">
+      <c r="B55" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" s="4">
         <v>1993</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="5">
         <v>13687924.0786476</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="6">
         <f t="shared" si="3"/>
         <v>-3.6842630268091314E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
+      <c r="A56" s="4">
         <v>2015</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D56" s="7">
+      <c r="B56" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" s="4">
         <v>1993</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="5">
         <v>14189502.6768736</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="6">
         <f t="shared" si="3"/>
         <v>3.6643876408434695E-2</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="7">
+      <c r="A57" s="4">
         <v>2016</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D57" s="7">
+      <c r="B57" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="4">
         <v>1993</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="5">
         <v>13373002.759948799</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="6">
         <f t="shared" si="3"/>
         <v>-5.754253235777973E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="7">
+      <c r="A58" s="4">
         <v>2017</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D58" s="7">
+      <c r="B58" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="4">
         <v>1993</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="5">
         <v>13655492.409271</v>
       </c>
-      <c r="F58" s="9">
+      <c r="F58" s="6">
         <f t="shared" si="3"/>
         <v>2.1123875796110525E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="7">
+      <c r="A59" s="4">
         <v>2018</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D59" s="7">
+      <c r="B59" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="4">
         <v>1993</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="5">
         <v>13585607.412423</v>
       </c>
-      <c r="F59" s="9">
+      <c r="F59" s="6">
         <f t="shared" si="3"/>
         <v>-5.1177207495317623E-3</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="7">
+      <c r="A60" s="4">
         <v>2019</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D60" s="7">
+      <c r="B60" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="4">
         <v>1993</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="5">
         <v>13410851.4459722</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="6">
         <f t="shared" si="3"/>
         <v>-1.2863316386648838E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="7">
+      <c r="A61" s="4">
         <v>2020</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D61" s="7">
+      <c r="B61" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="4">
         <v>1993</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="5">
         <v>12342645.8809737</v>
       </c>
-      <c r="F61" s="9">
+      <c r="F61" s="6">
         <f t="shared" si="3"/>
         <v>-7.9652330003202265E-2</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
+      <c r="A62" s="4">
         <v>2021</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D62" s="7">
+      <c r="B62" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="4">
         <v>1993</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="5">
         <v>13635887.646933099</v>
       </c>
-      <c r="F62" s="9">
+      <c r="F62" s="6">
         <f t="shared" si="3"/>
         <v>0.10477832536319798</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="7">
+      <c r="A63" s="4">
         <v>2022</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D63" s="7">
+      <c r="B63" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="4">
         <v>1993</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="5">
         <v>14178694.4422819</v>
       </c>
-      <c r="F63" s="9">
+      <c r="F63" s="6">
         <f t="shared" si="3"/>
         <v>3.9807221165457873E-2</v>
       </c>
@@ -3920,278 +3897,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>2004</v>
-      </c>
-      <c r="B5" s="8">
-        <v>18742164.978113499</v>
-      </c>
-      <c r="C5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>2005</v>
-      </c>
-      <c r="B6" s="8">
-        <v>21705292.3126196</v>
-      </c>
-      <c r="C6" s="9">
-        <f t="shared" ref="C6:C23" si="0">B6/B5-1</f>
-        <v>0.15809952254535942</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>2006</v>
-      </c>
-      <c r="B7" s="8">
-        <v>25989780.8096347</v>
-      </c>
-      <c r="C7" s="9">
-        <f t="shared" si="0"/>
-        <v>0.19739372477946637</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>2007</v>
-      </c>
-      <c r="B8" s="8">
-        <v>31491830.893817</v>
-      </c>
-      <c r="C8" s="9">
-        <f t="shared" si="0"/>
-        <v>0.21170051892637076</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>2008</v>
-      </c>
-      <c r="B9" s="8">
-        <v>38997291.515584901</v>
-      </c>
-      <c r="C9" s="9">
-        <f t="shared" si="0"/>
-        <v>0.23833039898742436</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>2009</v>
-      </c>
-      <c r="B10" s="8">
-        <v>42718111.124679796</v>
-      </c>
-      <c r="C10" s="9">
-        <f t="shared" si="0"/>
-        <v>9.5412257223246089E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>2010</v>
-      </c>
-      <c r="B11" s="8">
-        <v>53282204.423269801</v>
-      </c>
-      <c r="C11" s="9">
-        <f t="shared" si="0"/>
-        <v>0.24729776248198254</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>2011</v>
-      </c>
-      <c r="B12" s="8">
-        <v>66868626.278331898</v>
-      </c>
-      <c r="C12" s="9">
-        <f t="shared" si="0"/>
-        <v>0.25498986016292768</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>2012</v>
-      </c>
-      <c r="B13" s="8">
-        <v>80942510.660713002</v>
-      </c>
-      <c r="C13" s="9">
-        <f t="shared" si="0"/>
-        <v>0.21047066712273121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>2013</v>
-      </c>
-      <c r="B14" s="8">
-        <v>101855984.893814</v>
-      </c>
-      <c r="C14" s="9">
-        <f t="shared" si="0"/>
-        <v>0.25837441984921972</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>2014</v>
-      </c>
-      <c r="B15" s="8">
-        <v>132189446.004391</v>
-      </c>
-      <c r="C15" s="9">
-        <f t="shared" si="0"/>
-        <v>0.29780735164654271</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>2015</v>
-      </c>
-      <c r="B16" s="8">
-        <v>166195346.17819399</v>
-      </c>
-      <c r="C16" s="9">
-        <f t="shared" si="0"/>
-        <v>0.25725124963965285</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>2016</v>
-      </c>
-      <c r="B17" s="8">
-        <v>222509516.96513399</v>
-      </c>
-      <c r="C17" s="9">
-        <f t="shared" si="0"/>
-        <v>0.33884324731066884</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>2017</v>
-      </c>
-      <c r="B18" s="8">
-        <v>281052725.91586697</v>
-      </c>
-      <c r="C18" s="9">
-        <f t="shared" si="0"/>
-        <v>0.26310429211846409</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>2018</v>
-      </c>
-      <c r="B19" s="8">
-        <v>391618339.80809098</v>
-      </c>
-      <c r="C19" s="9">
-        <f t="shared" si="0"/>
-        <v>0.39339811963012883</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>2019</v>
-      </c>
-      <c r="B20" s="8">
-        <v>564916252.67370498</v>
-      </c>
-      <c r="C20" s="9">
-        <f t="shared" si="0"/>
-        <v>0.44251735746220944</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>2020</v>
-      </c>
-      <c r="B21" s="8">
-        <v>739953122.15121996</v>
-      </c>
-      <c r="C21" s="9">
-        <f t="shared" si="0"/>
-        <v>0.30984569597542833</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>2021</v>
-      </c>
-      <c r="B22" s="8">
-        <v>1166100443.59216</v>
-      </c>
-      <c r="C22" s="9">
-        <f t="shared" si="0"/>
-        <v>0.57591124178519348</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>2022</v>
-      </c>
-      <c r="B23" s="8">
-        <v>2209050309.26683</v>
-      </c>
-      <c r="C23" s="9">
-        <f t="shared" si="0"/>
-        <v>0.89439110619139628</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4201,432 +3906,432 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="3"/>
+      <c r="A1" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="21"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>42</v>
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="4">
         <v>1970</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>4.7536083333333301E-10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="4">
         <v>1971</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>6.4042000000000005E-10</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="4">
         <v>1972</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>1.0147766666666699E-9</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="4">
         <v>1973</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>1.62672083333333E-9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="4">
         <v>1974</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>2.02065416666667E-9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="4">
         <v>1975</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>5.71426666666667E-9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="4">
         <v>1976</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>3.1086300000000001E-8</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="4">
         <v>1977</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>8.5808050000000006E-8</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="4">
         <v>1978</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>2.3640875E-7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="4">
         <v>1979</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>6.1350683333333398E-7</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="4">
         <v>1980</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="7">
         <v>1.2317020000000001E-6</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="4">
         <v>1981</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="7">
         <v>2.5185499999999998E-6</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="4">
         <v>1982</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <v>6.6685833333333299E-6</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="4">
         <v>1983</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>2.95951416666667E-5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="4">
         <v>1984</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="7">
         <v>2.1507783333333299E-4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="4">
         <v>1985</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>1.6607925000000001E-3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="4">
         <v>1986</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>3.1570041666666702E-3</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="4">
         <v>1987</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="7">
         <v>7.30324166666667E-3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="4">
         <v>1988</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="7">
         <v>3.2349999999999997E-2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="4">
         <v>1989</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="7">
         <v>1.0285535833333299</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="4">
         <v>1990</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="7">
         <v>24.828900000000001</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="4">
         <v>1991</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="7">
         <v>67.453100000000006</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="4">
         <v>1992</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="7">
         <v>84.248900000000006</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="4">
         <v>1993</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="7">
         <v>93.188999999999993</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="4">
         <v>1994</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="7">
         <v>97.081800000000001</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="4">
         <v>1995</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="7">
         <v>100.35939999999999</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="4">
         <v>1996</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="7">
         <v>100.51560000000001</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="4">
         <v>1997</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="7">
         <v>101.04689999999999</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32" s="4">
         <v>1998</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="7">
         <v>101.9813</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33" s="4">
         <v>1999</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="7">
         <v>100.7915</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34" s="4">
         <v>2000</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="7">
         <v>99.844899999999996</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
+      <c r="A35" s="4">
         <v>2001</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="7">
         <v>98.781666666666695</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
+      <c r="A36" s="4">
         <v>2002</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="7">
         <v>124.33499999999999</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
+      <c r="A37" s="4">
         <v>2003</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="7">
         <v>141.05000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
+      <c r="A38" s="4">
         <v>2004</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="7">
         <v>147.28</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
+      <c r="A39" s="4">
         <v>2005</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="7">
         <v>167.48</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40" s="4">
         <v>2006</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="7">
         <v>179.08</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
+      <c r="A41" s="4">
         <v>2007</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="7">
         <v>194.89</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
+      <c r="A42" s="4">
         <v>2008</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="7">
         <v>238.54535999999999</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
+      <c r="A43" s="4">
         <v>2009</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="7">
         <v>287.92424951999999</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
+      <c r="A44" s="4">
         <v>2010</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="7">
         <v>334.56797794224002</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
+      <c r="A45" s="4">
         <v>2011</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="7">
         <v>427.91244378812502</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
+      <c r="A46" s="4">
         <v>2012</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="7">
         <v>527.61604319075798</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
+      <c r="A47" s="4">
         <v>2013</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="7">
         <v>650.55058125420499</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
+      <c r="A48" s="4">
         <v>2014</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="7">
         <v>844.41465446795803</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
+      <c r="A49" s="4">
         <v>2015</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="7">
         <v>1192.3134921087601</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
+      <c r="A50" s="4">
         <v>2016</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="7">
         <v>1513.04582148601</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
+      <c r="A51" s="4">
         <v>2017</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="7">
         <v>2066.8205921498902</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
+      <c r="A52" s="4">
         <v>2018</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="7">
         <v>2546.32296952867</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
+      <c r="A53" s="4">
         <v>2019</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="7">
         <v>3860.2256218054599</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
+      <c r="A54" s="4">
         <v>2020</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="7">
         <v>5921.5861038495796</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
+      <c r="A55" s="4">
         <v>2021</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="7">
         <v>8136.2593066893196</v>
       </c>
     </row>
@@ -4639,7 +4344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4649,74 +4354,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="A1" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="A3" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="11">
+      <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="8">
         <f>'PBG por tramo'!E33/'PBG por tramo'!E29</f>
         <v>26.136104337887964</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>46</v>
+      <c r="A7" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="11">
+      <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="8">
         <f>'IPC INDEC'!B33/'IPC INDEC'!B27</f>
         <v>1.0815815171318504</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>48</v>
+      <c r="A10" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4729,260 +4434,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>1970</v>
-      </c>
-      <c r="B5" s="8">
-        <f>'PBG por tramo'!E5</f>
-        <v>313.43</v>
-      </c>
-      <c r="C5" s="8">
-        <f t="shared" ref="C5:C20" si="0">B5/B$5*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>1971</v>
-      </c>
-      <c r="B6" s="8">
-        <f>'PBG por tramo'!E6</f>
-        <v>334.41</v>
-      </c>
-      <c r="C6" s="8">
-        <f t="shared" si="0"/>
-        <v>106.69367960948219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>1972</v>
-      </c>
-      <c r="B7" s="8">
-        <f>'PBG por tramo'!E7</f>
-        <v>356.26</v>
-      </c>
-      <c r="C7" s="8">
-        <f t="shared" si="0"/>
-        <v>113.66493315891906</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>1973</v>
-      </c>
-      <c r="B8" s="8">
-        <f>'PBG por tramo'!E8</f>
-        <v>364.33</v>
-      </c>
-      <c r="C8" s="8">
-        <f t="shared" si="0"/>
-        <v>116.23967073987811</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>1974</v>
-      </c>
-      <c r="B9" s="8">
-        <f>'PBG por tramo'!E9</f>
-        <v>406.37</v>
-      </c>
-      <c r="C9" s="8">
-        <f t="shared" si="0"/>
-        <v>129.65255399929811</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>1975</v>
-      </c>
-      <c r="B10" s="8">
-        <f>'PBG por tramo'!E10</f>
-        <v>355.2</v>
-      </c>
-      <c r="C10" s="8">
-        <f t="shared" si="0"/>
-        <v>113.32673962288229</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>1976</v>
-      </c>
-      <c r="B11" s="8">
-        <f>'PBG por tramo'!E11</f>
-        <v>404.05</v>
-      </c>
-      <c r="C11" s="8">
-        <f t="shared" si="0"/>
-        <v>128.91235682608558</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>1977</v>
-      </c>
-      <c r="B12" s="8">
-        <f>'PBG por tramo'!E12</f>
-        <v>380.63</v>
-      </c>
-      <c r="C12" s="8">
-        <f t="shared" si="0"/>
-        <v>121.44019398270747</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>1978</v>
-      </c>
-      <c r="B13" s="8">
-        <f>'PBG por tramo'!E13</f>
-        <v>423.6</v>
-      </c>
-      <c r="C13" s="8">
-        <f t="shared" si="0"/>
-        <v>135.14979421242384</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>1979</v>
-      </c>
-      <c r="B14" s="8">
-        <f>'PBG por tramo'!E14</f>
-        <v>481.05</v>
-      </c>
-      <c r="C14" s="8">
-        <f t="shared" si="0"/>
-        <v>153.47924576460454</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>1980</v>
-      </c>
-      <c r="B15" s="8">
-        <f>'PBG por tramo'!E15</f>
-        <v>429.24</v>
-      </c>
-      <c r="C15" s="8">
-        <f t="shared" si="0"/>
-        <v>136.94923906454392</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>1981</v>
-      </c>
-      <c r="B16" s="8">
-        <f>'PBG por tramo'!E16</f>
-        <v>351.83</v>
-      </c>
-      <c r="C16" s="8">
-        <f t="shared" si="0"/>
-        <v>112.25153941868997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>1982</v>
-      </c>
-      <c r="B17" s="8">
-        <f>'PBG por tramo'!E17</f>
-        <v>360.43</v>
-      </c>
-      <c r="C17" s="8">
-        <f t="shared" si="0"/>
-        <v>114.99537376766742</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>1983</v>
-      </c>
-      <c r="B18" s="8">
-        <f>'PBG por tramo'!E18</f>
-        <v>419.26</v>
-      </c>
-      <c r="C18" s="8">
-        <f t="shared" si="0"/>
-        <v>133.7651150177073</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>1984</v>
-      </c>
-      <c r="B19" s="8">
-        <f>'PBG por tramo'!E19</f>
-        <v>404.44</v>
-      </c>
-      <c r="C19" s="8">
-        <f t="shared" si="0"/>
-        <v>129.03678652330663</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>1985</v>
-      </c>
-      <c r="B20" s="8">
-        <f>'PBG por tramo'!E20</f>
-        <v>384.61</v>
-      </c>
-      <c r="C20" s="8">
-        <f t="shared" si="0"/>
-        <v>122.71001499537377</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4992,310 +4444,310 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="3"/>
+      <c r="A1" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="21"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="2"/>
+      <c r="A2" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="22"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>56</v>
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="4">
         <v>1969</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="5">
         <v>152643.77335610599</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="4">
         <v>1970</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="5">
         <v>160860.95636173099</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="4">
         <v>1971</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="5">
         <v>166912.606221553</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="4">
         <v>1972</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="5">
         <v>170379.33445085399</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="4">
         <v>1973</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="5">
         <v>176760.97430606201</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="4">
         <v>1974</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="5">
         <v>186316.01795022801</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="4">
         <v>1975</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="5">
         <v>185210.551465686</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="4">
         <v>1976</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="5">
         <v>185188.55213266</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="4">
         <v>1977</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="5">
         <v>197015.02691173099</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="4">
         <v>1978</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="5">
         <v>190666.38605606201</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="4">
         <v>1979</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="5">
         <v>203891.651760017</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="4">
         <v>1980</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="5">
         <v>207011.43217472499</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="4">
         <v>1981</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="5">
         <v>195787.085571267</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="4">
         <v>1982</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="5">
         <v>189602.24152446401</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="4">
         <v>1983</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="5">
         <v>197400.610512652</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="4">
         <v>1984</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="5">
         <v>201349.024597112</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="4">
         <v>1985</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="5">
         <v>187351.74596487399</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="4">
         <v>1986</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="5">
         <v>200726.11957615399</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="4">
         <v>1987</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="5">
         <v>205926.37181563699</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="4">
         <v>1988</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="5">
         <v>202022.16389395401</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="4">
         <v>1989</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="5">
         <v>188010.819664468</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="4">
         <v>1990</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="5">
         <v>184568.767080916</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="4">
         <v>1991</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="5">
         <v>204093.82543139899</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="4">
         <v>1992</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="5">
         <v>223701.26799433099</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="4">
         <v>1993</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="5">
         <v>236504.98023157299</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="4">
         <v>1994</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="5">
         <v>250307.88553631501</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="4">
         <v>1995</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="5">
         <v>243186.10151946</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32" s="4">
         <v>1996</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="5">
         <v>256626.24305584701</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33" s="4">
         <v>1997</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="5">
         <v>277441.31762237998</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34" s="4">
         <v>1998</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="5">
         <v>288122.80460772401</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
+      <c r="A35" s="4">
         <v>1999</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="5">
         <v>278369.01387171802</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
+      <c r="A36" s="4">
         <v>2000</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="5">
         <v>276172.18535265001</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
+      <c r="A37" s="4">
         <v>2001</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="5">
         <v>263995.67436681699</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
+      <c r="A38" s="4">
         <v>2002</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="5">
         <v>235234.596752907</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
+      <c r="A39" s="4">
         <v>2003</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="5">
         <v>256022.46524751</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40" s="4">
         <v>2004</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="5">
         <v>279020</v>
       </c>
     </row>
@@ -5309,7 +4761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5319,63 +4771,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="A1" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="A3" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="9">
         <f>'PBI Ferreres (nacional)'!B22/'PBI Ferreres (nacional)'!B21-1</f>
         <v>7.1386437005970027E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="10">
         <f>'PBG por tramo'!E22/('PBG por tramo'!E20*(1+B5))</f>
         <v>649.43174288959028</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5388,7 +4840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5400,876 +4852,876 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="A1" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="A2" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>30</v>
+      <c r="A4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="11">
         <v>1970</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="8">
+      <c r="B5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="5">
         <f>'PBG por tramo'!E5*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>5754057.3647016427</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="11">
         <v>1971</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5">
         <f>'PBG por tramo'!E6*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>6139215.5292405849</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="13">
         <f t="shared" ref="D6:D37" si="0">C6/C5-1</f>
         <v>6.6936796094821949E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="11">
         <v>1972</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="5">
         <f>'PBG por tramo'!E7*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>6540345.4575139806</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="13">
         <f t="shared" si="0"/>
         <v>6.5338955174785163E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="11">
         <v>1973</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="5">
         <f>'PBG por tramo'!E8*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>6688497.3349128971</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="13">
         <f t="shared" si="0"/>
         <v>2.2651995733453223E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="11">
         <v>1974</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="8">
+      <c r="B9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="5">
         <f>'PBG por tramo'!E9*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7460282.3319203863</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="13">
         <f t="shared" si="0"/>
         <v>0.11538989377761943</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="11">
         <v>1975</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="8">
+      <c r="B10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="5">
         <f>'PBG por tramo'!E10*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>6520885.6074467134</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="13">
         <f t="shared" si="0"/>
         <v>-0.12591972832640219</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="11">
         <v>1976</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="8">
+      <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="5">
         <f>'PBG por tramo'!E11*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7417690.9619618375</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="13">
         <f t="shared" si="0"/>
         <v>0.13752815315315314</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="14">
+      <c r="A12" s="11">
         <v>1977</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="8">
+      <c r="B12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="5">
         <f>'PBG por tramo'!E12*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>6987738.4255699394</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="13">
         <f t="shared" si="0"/>
         <v>-5.7963123375819881E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="14">
+      <c r="A13" s="11">
         <v>1978</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="B13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="5">
         <f>'PBG por tramo'!E13*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7776596.6872590873</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="13">
         <f t="shared" si="0"/>
         <v>0.11289178467277927</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
+      <c r="A14" s="11">
         <v>1979</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="8">
+      <c r="B14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="5">
         <f>'PBG por tramo'!E14*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>8831283.8442067616</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="13">
         <f t="shared" si="0"/>
         <v>0.13562322946175653</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="14">
+      <c r="A15" s="11">
         <v>1980</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="8">
+      <c r="B15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="5">
         <f>'PBG por tramo'!E15*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7880137.7762962487</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="13">
         <f t="shared" si="0"/>
         <v>-0.10770190208917985</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="14">
+      <c r="A16" s="11">
         <v>1981</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="8">
+      <c r="B16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="5">
         <f>'PBG por tramo'!E16*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>6459017.970912097</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="13">
         <f t="shared" si="0"/>
         <v>-0.18034199981362431</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
+      <c r="A17" s="11">
         <v>1982</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="8">
+      <c r="B17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="5">
         <f>'PBG por tramo'!E17*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>6616899.7733446481</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="13">
         <f t="shared" si="0"/>
         <v>2.4443623340818288E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
+      <c r="A18" s="11">
         <v>1983</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="B18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="5">
         <f>'PBG por tramo'!E18*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7696921.452078009</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="13">
         <f t="shared" si="0"/>
         <v>0.16322170740504371</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="14">
+      <c r="A19" s="11">
         <v>1984</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="8">
+      <c r="B19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="5">
         <f>'PBG por tramo'!E19*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7424850.7181186629</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="13">
         <f t="shared" si="0"/>
         <v>-3.5347994084815926E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="14">
+      <c r="A20" s="11">
         <v>1985</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="8">
+      <c r="B20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="5">
         <f>'PBG por tramo'!E20*'Coeficiente de empalme (A-B)'!$B$7*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7060804.655067794</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="13">
         <f t="shared" si="0"/>
         <v>-4.9030758579764688E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="14">
+      <c r="A21" s="11">
         <v>1986</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="8">
+      <c r="B21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="5">
         <f>'PBG por tramo'!E22*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7564850.341788251</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="13">
         <f t="shared" si="0"/>
         <v>7.1386437005970027E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+      <c r="A22" s="11">
         <v>1987</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="8">
+      <c r="B22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="5">
         <f>'PBG por tramo'!E23*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7662186.6734616216</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="13">
         <f t="shared" si="0"/>
         <v>1.2866920993226394E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="14">
+      <c r="A23" s="11">
         <v>1988</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="8">
+      <c r="B23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="5">
         <f>'PBG por tramo'!E24*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7476209.3476174874</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="13">
         <f t="shared" si="0"/>
         <v>-2.4272095391290383E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="14">
+      <c r="A24" s="11">
         <v>1989</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="8">
+      <c r="B24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="5">
         <f>'PBG por tramo'!E25*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7163476.8417938603</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="13">
         <f t="shared" si="0"/>
         <v>-4.1830356974057792E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="14">
+      <c r="A25" s="11">
         <v>1990</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="8">
+      <c r="B25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="5">
         <f>'PBG por tramo'!E26*'Coeficiente de empalme (B-C)'!$B$5*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7169611.0688356869</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="13">
         <f t="shared" si="0"/>
         <v>8.5631979795586233E-4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="14">
+      <c r="A26" s="11">
         <v>1991</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="8">
+      <c r="B26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="5">
         <f>'PBG por tramo'!E31*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7014604.4430224905</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="13">
         <f t="shared" si="0"/>
         <v>-2.1619949021637663E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="14">
+      <c r="A27" s="11">
         <v>1992</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="8">
+      <c r="B27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="5">
         <f>'PBG por tramo'!E32*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>7608953.647225867</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="13">
         <f t="shared" si="0"/>
         <v>8.4730252294494379E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="14">
+      <c r="A28" s="11">
         <v>1993</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="8">
+      <c r="B28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="5">
         <f>'PBG por tramo'!E33*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>8394703.8409033343</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="13">
         <f t="shared" si="0"/>
         <v>0.10326652390160662</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="14">
+      <c r="A29" s="11">
         <v>1994</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="8">
+      <c r="B29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="5">
         <f>'PBG por tramo'!E34*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>8758677.7459252588</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="13">
         <f t="shared" si="0"/>
         <v>4.3357563520997067E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="14">
+      <c r="A30" s="11">
         <v>1995</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="8">
+      <c r="B30" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="5">
         <f>'PBG por tramo'!E35*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>8554024.2171968576</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="13">
         <f t="shared" si="0"/>
         <v>-2.336580185560666E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="14">
+      <c r="A31" s="11">
         <v>1996</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="8">
+      <c r="B31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="5">
         <f>'PBG por tramo'!E36*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>8799057.0415878613</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="13">
         <f t="shared" si="0"/>
         <v>2.8645327411909172E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="14">
+      <c r="A32" s="11">
         <v>1997</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="8">
+      <c r="B32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="5">
         <f>'PBG por tramo'!E37*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>9632521.1279348768</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="13">
         <f t="shared" si="0"/>
         <v>9.4721977867370466E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="14">
+      <c r="A33" s="11">
         <v>1998</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="8">
+      <c r="B33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="5">
         <f>'PBG por tramo'!E38*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>10262365.509435022</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="13">
         <f t="shared" si="0"/>
         <v>6.5387282637103139E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="14">
+      <c r="A34" s="11">
         <v>1999</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="8">
+      <c r="B34" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="5">
         <f>'PBG por tramo'!E39*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>10007457.552320169</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="13">
         <f t="shared" si="0"/>
         <v>-2.4839103312047861E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="14">
+      <c r="A35" s="11">
         <v>2000</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="8">
+      <c r="B35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="5">
         <f>'PBG por tramo'!E40*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>9736438.4054777417</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="13">
         <f t="shared" si="0"/>
         <v>-2.7081718351090411E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="14">
+      <c r="A36" s="11">
         <v>2001</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="8">
+      <c r="B36" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="5">
         <f>'PBG por tramo'!E41*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>9001995.9332073387</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="13">
         <f t="shared" si="0"/>
         <v>-7.5432354387124145E-2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="14">
+      <c r="A37" s="11">
         <v>2002</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" s="8">
+      <c r="B37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="5">
         <f>'PBG por tramo'!E42*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>8406265.7469327673</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="13">
         <f t="shared" si="0"/>
         <v>-6.6177566696846712E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="14">
+      <c r="A38" s="11">
         <v>2003</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="8">
+      <c r="B38" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="5">
         <f>'PBG por tramo'!E43*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>10101895.220762277</v>
       </c>
-      <c r="D38" s="16">
-        <f t="shared" ref="D38:D69" si="1">C38/C37-1</f>
+      <c r="D38" s="13">
+        <f t="shared" ref="D38:D57" si="1">C38/C37-1</f>
         <v>0.20171019152567249</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="14">
+      <c r="A39" s="11">
         <v>2004</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="8">
+      <c r="B39" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="5">
         <f>'PBG por tramo'!E45*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>11762122.311525308</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="13">
         <f t="shared" si="1"/>
         <v>0.16434808068002815</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="14">
+      <c r="A40" s="11">
         <v>2005</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="8">
+      <c r="B40" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="5">
         <f>'PBG por tramo'!E46*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>12309223.356326474</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="13">
         <f t="shared" si="1"/>
         <v>4.6513803403071208E-2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="14">
+      <c r="A41" s="11">
         <v>2006</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C41" s="8">
+      <c r="B41" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="5">
         <f>'PBG por tramo'!E47*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>13259436.594352694</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="13">
         <f t="shared" si="1"/>
         <v>7.7195222681360143E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="14">
+      <c r="A42" s="11">
         <v>2007</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="8">
+      <c r="B42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="5">
         <f>'PBG por tramo'!E48*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>13812573.217410319</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="13">
         <f t="shared" si="1"/>
         <v>4.1716449950309986E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="14">
+      <c r="A43" s="11">
         <v>2008</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="8">
+      <c r="B43" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="5">
         <f>'PBG por tramo'!E49*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14131050.687456433</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="13">
         <f t="shared" si="1"/>
         <v>2.3057070180426908E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="14">
+      <c r="A44" s="11">
         <v>2009</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="8">
+      <c r="B44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" s="5">
         <f>'PBG por tramo'!E50*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>13736909.129691008</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="13">
         <f t="shared" si="1"/>
         <v>-2.7891879130777397E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="14">
+      <c r="A45" s="11">
         <v>2010</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" s="8">
+      <c r="B45" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="5">
         <f>'PBG por tramo'!E51*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14344401.024201935</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="13">
         <f t="shared" si="1"/>
         <v>4.4223332102990343E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="14">
+      <c r="A46" s="11">
         <v>2011</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C46" s="8">
+      <c r="B46" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="5">
         <f>'PBG por tramo'!E52*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14860479.787137467</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="13">
         <f t="shared" si="1"/>
         <v>3.5977714375441838E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="14">
+      <c r="A47" s="11">
         <v>2012</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C47" s="8">
+      <c r="B47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="5">
         <f>'PBG por tramo'!E53*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14650114.275526542</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="13">
         <f t="shared" si="1"/>
         <v>-1.4156037666630872E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="14">
+      <c r="A48" s="11">
         <v>2013</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C48" s="8">
+      <c r="B48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="5">
         <f>'PBG por tramo'!E54*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>15370910.462420139</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="13">
         <f t="shared" si="1"/>
         <v>4.9200721123227709E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="14">
+      <c r="A49" s="11">
         <v>2014</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="8">
+      <c r="B49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="5">
         <f>'PBG por tramo'!E55*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14804605.691369256</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="13">
         <f t="shared" si="1"/>
         <v>-3.6842630268091425E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="14">
+      <c r="A50" s="11">
         <v>2015</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C50" s="8">
+      <c r="B50" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="5">
         <f>'PBG por tramo'!E56*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>15347103.8325994</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="13">
         <f t="shared" si="1"/>
         <v>3.6643876408434695E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="14">
+      <c r="A51" s="11">
         <v>2016</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="8">
+      <c r="B51" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="5">
         <f>'PBG por tramo'!E57*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14463992.613713844</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="13">
         <f t="shared" si="1"/>
         <v>-5.754253235777973E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="14">
+      <c r="A52" s="11">
         <v>2017</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C52" s="8">
+      <c r="B52" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="5">
         <f>'PBG por tramo'!E58*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14769528.197201794</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="13">
         <f t="shared" si="1"/>
         <v>2.1123875796110525E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="14">
+      <c r="A53" s="11">
         <v>2018</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C53" s="8">
+      <c r="B53" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="5">
         <f>'PBG por tramo'!E59*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14693941.876286181</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="13">
         <f t="shared" si="1"/>
         <v>-5.1177207495317623E-3</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="14">
+      <c r="A54" s="11">
         <v>2019</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C54" s="8">
+      <c r="B54" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="5">
         <f>'PBG por tramo'!E60*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14504929.052964482</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="13">
         <f t="shared" si="1"/>
         <v>-1.2863316386648838E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="14">
+      <c r="A55" s="11">
         <v>2020</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C55" s="8">
+      <c r="B55" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="5">
         <f>'PBG por tramo'!E61*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>13349577.657364719</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="13">
         <f t="shared" si="1"/>
         <v>-7.9652330003202265E-2</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="14">
+      <c r="A56" s="11">
         <v>2021</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" s="8">
+      <c r="B56" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="5">
         <f>'PBG por tramo'!E62*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>14748324.048609359</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="13">
         <f t="shared" si="1"/>
         <v>0.1047783253631982</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="20">
+      <c r="A57" s="17">
         <v>2022</v>
       </c>
-      <c r="B57" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" s="22">
+      <c r="B57" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" s="19">
         <f>'PBG por tramo'!E63*'Coeficiente de empalme (B-C)'!$B$8</f>
         <v>15335413.845832191</v>
       </c>
-      <c r="D57" s="23">
+      <c r="D57" s="20">
         <f t="shared" si="1"/>
         <v>3.9807221165457873E-2</v>
       </c>

--- a/PBG_Mendoza_1970-2022_ordenado.xlsx
+++ b/PBG_Mendoza_1970-2022_ordenado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Facultad\Proyecto-evolucion-salarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/971a82d91f2470ed/Escritorio/ECONOMIA/3 AÑO/Lab Ciencia de Datos/Proyecto historia economica/Proyecto-evolucion-salarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95B218E-9BA0-4EAA-B509-1EFB85E5B91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{A95B218E-9BA0-4EAA-B509-1EFB85E5B91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B35EC291-FDAE-4AFD-8BC9-1BA11580ED43}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,17 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -415,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -474,6 +485,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2561,19 +2573,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21"/>
     </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2581,7 +2593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2589,7 +2601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -2597,7 +2609,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -2605,7 +2617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -2613,7 +2625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -2621,7 +2633,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -2629,7 +2641,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
@@ -2637,7 +2649,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -2645,7 +2657,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -2653,7 +2665,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -2673,7 +2685,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2682,7 +2694,7 @@
     <col min="5" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>20</v>
       </c>
@@ -2692,7 +2704,7 @@
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>62</v>
       </c>
@@ -2702,7 +2714,7 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
@@ -2722,7 +2734,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>1970</v>
       </c>
@@ -2740,7 +2752,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>1971</v>
       </c>
@@ -2761,7 +2773,7 @@
         <v>6.6936796094821949E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>1972</v>
       </c>
@@ -2782,7 +2794,7 @@
         <v>6.5338955174785385E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>1973</v>
       </c>
@@ -2803,7 +2815,7 @@
         <v>2.2651995733453001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>1974</v>
       </c>
@@ -2824,7 +2836,7 @@
         <v>0.11538989377761921</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>1975</v>
       </c>
@@ -2845,7 +2857,7 @@
         <v>-0.12591972832640208</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>1976</v>
       </c>
@@ -2866,7 +2878,7 @@
         <v>0.13752815315315314</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>1977</v>
       </c>
@@ -2887,7 +2899,7 @@
         <v>-5.7963123375819881E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>1978</v>
       </c>
@@ -2908,7 +2920,7 @@
         <v>0.11289178467277949</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>1979</v>
       </c>
@@ -2929,7 +2941,7 @@
         <v>0.13562322946175631</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>1980</v>
       </c>
@@ -2950,7 +2962,7 @@
         <v>-0.10770190208917996</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>1981</v>
       </c>
@@ -2971,7 +2983,7 @@
         <v>-0.18034199981362409</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>1982</v>
       </c>
@@ -2992,7 +3004,7 @@
         <v>2.4443623340818066E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>1983</v>
       </c>
@@ -3013,7 +3025,7 @@
         <v>0.16322170740504394</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>1984</v>
       </c>
@@ -3034,7 +3046,7 @@
         <v>-3.5347994084816037E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>1985</v>
       </c>
@@ -3055,7 +3067,7 @@
         <v>-4.9030758579764577E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>1986</v>
       </c>
@@ -3073,7 +3085,7 @@
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>1987</v>
       </c>
@@ -3094,7 +3106,7 @@
         <v>1.2866920993226172E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>1988</v>
       </c>
@@ -3115,7 +3127,7 @@
         <v>-2.4272095391290271E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>1989</v>
       </c>
@@ -3136,7 +3148,7 @@
         <v>-4.1830356974057792E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>1990</v>
       </c>
@@ -3157,7 +3169,7 @@
         <v>8.5631979795586233E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>1991</v>
       </c>
@@ -3178,7 +3190,7 @@
         <v>2.3467533030789411E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>1992</v>
       </c>
@@ -3199,7 +3211,7 @@
         <v>6.891928854029028E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>1993</v>
       </c>
@@ -3220,7 +3232,7 @@
         <v>7.0263705134627763E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>1991</v>
       </c>
@@ -3238,7 +3250,7 @@
       </c>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>1992</v>
       </c>
@@ -3259,7 +3271,7 @@
         <v>8.4730252294494379E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>1993</v>
       </c>
@@ -3280,7 +3292,7 @@
         <v>0.10326652390160662</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>1994</v>
       </c>
@@ -3301,7 +3313,7 @@
         <v>4.3357563520997067E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>1995</v>
       </c>
@@ -3322,7 +3334,7 @@
         <v>-2.3365801855606549E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>1996</v>
       </c>
@@ -3343,7 +3355,7 @@
         <v>2.8645327411909172E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>1997</v>
       </c>
@@ -3364,7 +3376,7 @@
         <v>9.4721977867370466E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>1998</v>
       </c>
@@ -3385,7 +3397,7 @@
         <v>6.5387282637103139E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>1999</v>
       </c>
@@ -3406,7 +3418,7 @@
         <v>-2.483910331204775E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>2000</v>
       </c>
@@ -3427,7 +3439,7 @@
         <v>-2.7081718351090522E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>2001</v>
       </c>
@@ -3448,7 +3460,7 @@
         <v>-7.5432354387124145E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>2002</v>
       </c>
@@ -3469,7 +3481,7 @@
         <v>-6.6177566696846712E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>2003</v>
       </c>
@@ -3490,7 +3502,7 @@
         <v>0.20171019152567271</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>2004</v>
       </c>
@@ -3508,7 +3520,7 @@
       </c>
       <c r="F45" s="4"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>2005</v>
       </c>
@@ -3529,7 +3541,7 @@
         <v>4.6513803403071208E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>2006</v>
       </c>
@@ -3550,7 +3562,7 @@
         <v>7.7195222681360143E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>2007</v>
       </c>
@@ -3571,7 +3583,7 @@
         <v>4.1716449950309986E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>2008</v>
       </c>
@@ -3592,7 +3604,7 @@
         <v>2.3057070180426908E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>2009</v>
       </c>
@@ -3613,7 +3625,7 @@
         <v>-2.7891879130777508E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>2010</v>
       </c>
@@ -3634,7 +3646,7 @@
         <v>4.4223332102990343E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>2011</v>
       </c>
@@ -3655,7 +3667,7 @@
         <v>3.5977714375441838E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>2012</v>
       </c>
@@ -3676,7 +3688,7 @@
         <v>-1.4156037666630872E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>2013</v>
       </c>
@@ -3697,7 +3709,7 @@
         <v>4.9200721123227487E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>2014</v>
       </c>
@@ -3718,7 +3730,7 @@
         <v>-3.6842630268091314E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>2015</v>
       </c>
@@ -3739,7 +3751,7 @@
         <v>3.6643876408434695E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>2016</v>
       </c>
@@ -3760,7 +3772,7 @@
         <v>-5.754253235777973E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>2017</v>
       </c>
@@ -3781,7 +3793,7 @@
         <v>2.1123875796110525E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>2018</v>
       </c>
@@ -3802,7 +3814,7 @@
         <v>-5.1177207495317623E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>2019</v>
       </c>
@@ -3823,7 +3835,7 @@
         <v>-1.2863316386648838E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>2020</v>
       </c>
@@ -3844,7 +3856,7 @@
         <v>-7.9652330003202265E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>2021</v>
       </c>
@@ -3865,7 +3877,7 @@
         <v>0.10477832536319798</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>2022</v>
       </c>
@@ -3899,19 +3911,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="21"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>21</v>
       </c>
@@ -3919,7 +3931,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>1970</v>
       </c>
@@ -3927,7 +3939,7 @@
         <v>4.7536083333333301E-10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>1971</v>
       </c>
@@ -3935,7 +3947,7 @@
         <v>6.4042000000000005E-10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>1972</v>
       </c>
@@ -3943,7 +3955,7 @@
         <v>1.0147766666666699E-9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>1973</v>
       </c>
@@ -3951,7 +3963,7 @@
         <v>1.62672083333333E-9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>1974</v>
       </c>
@@ -3959,7 +3971,7 @@
         <v>2.02065416666667E-9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>1975</v>
       </c>
@@ -3967,7 +3979,7 @@
         <v>5.71426666666667E-9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>1976</v>
       </c>
@@ -3975,7 +3987,7 @@
         <v>3.1086300000000001E-8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>1977</v>
       </c>
@@ -3983,7 +3995,7 @@
         <v>8.5808050000000006E-8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>1978</v>
       </c>
@@ -3991,7 +4003,7 @@
         <v>2.3640875E-7</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>1979</v>
       </c>
@@ -3999,7 +4011,7 @@
         <v>6.1350683333333398E-7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>1980</v>
       </c>
@@ -4007,7 +4019,7 @@
         <v>1.2317020000000001E-6</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>1981</v>
       </c>
@@ -4015,7 +4027,7 @@
         <v>2.5185499999999998E-6</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>1982</v>
       </c>
@@ -4023,7 +4035,7 @@
         <v>6.6685833333333299E-6</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>1983</v>
       </c>
@@ -4031,7 +4043,7 @@
         <v>2.95951416666667E-5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>1984</v>
       </c>
@@ -4039,7 +4051,7 @@
         <v>2.1507783333333299E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>1985</v>
       </c>
@@ -4047,7 +4059,7 @@
         <v>1.6607925000000001E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>1986</v>
       </c>
@@ -4055,7 +4067,7 @@
         <v>3.1570041666666702E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>1987</v>
       </c>
@@ -4063,7 +4075,7 @@
         <v>7.30324166666667E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>1988</v>
       </c>
@@ -4071,7 +4083,7 @@
         <v>3.2349999999999997E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>1989</v>
       </c>
@@ -4079,7 +4091,7 @@
         <v>1.0285535833333299</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>1990</v>
       </c>
@@ -4087,7 +4099,7 @@
         <v>24.828900000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>1991</v>
       </c>
@@ -4095,7 +4107,7 @@
         <v>67.453100000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>1992</v>
       </c>
@@ -4103,7 +4115,7 @@
         <v>84.248900000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>1993</v>
       </c>
@@ -4111,7 +4123,7 @@
         <v>93.188999999999993</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>1994</v>
       </c>
@@ -4119,7 +4131,7 @@
         <v>97.081800000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>1995</v>
       </c>
@@ -4127,7 +4139,7 @@
         <v>100.35939999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>1996</v>
       </c>
@@ -4135,7 +4147,7 @@
         <v>100.51560000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>1997</v>
       </c>
@@ -4143,7 +4155,7 @@
         <v>101.04689999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>1998</v>
       </c>
@@ -4151,7 +4163,7 @@
         <v>101.9813</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>1999</v>
       </c>
@@ -4159,7 +4171,7 @@
         <v>100.7915</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>2000</v>
       </c>
@@ -4167,7 +4179,7 @@
         <v>99.844899999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>2001</v>
       </c>
@@ -4175,7 +4187,7 @@
         <v>98.781666666666695</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>2002</v>
       </c>
@@ -4183,7 +4195,7 @@
         <v>124.33499999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>2003</v>
       </c>
@@ -4191,7 +4203,7 @@
         <v>141.05000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>2004</v>
       </c>
@@ -4199,7 +4211,7 @@
         <v>147.28</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>2005</v>
       </c>
@@ -4207,7 +4219,7 @@
         <v>167.48</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>2006</v>
       </c>
@@ -4215,7 +4227,7 @@
         <v>179.08</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>2007</v>
       </c>
@@ -4223,7 +4235,7 @@
         <v>194.89</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>2008</v>
       </c>
@@ -4231,7 +4243,7 @@
         <v>238.54535999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>2009</v>
       </c>
@@ -4239,7 +4251,7 @@
         <v>287.92424951999999</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>2010</v>
       </c>
@@ -4247,7 +4259,7 @@
         <v>334.56797794224002</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>2011</v>
       </c>
@@ -4255,7 +4267,7 @@
         <v>427.91244378812502</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>2012</v>
       </c>
@@ -4263,7 +4275,7 @@
         <v>527.61604319075798</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>2013</v>
       </c>
@@ -4271,7 +4283,7 @@
         <v>650.55058125420499</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>2014</v>
       </c>
@@ -4279,7 +4291,7 @@
         <v>844.41465446795803</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>2015</v>
       </c>
@@ -4287,7 +4299,7 @@
         <v>1192.3134921087601</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>2016</v>
       </c>
@@ -4295,7 +4307,7 @@
         <v>1513.04582148601</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>2017</v>
       </c>
@@ -4303,7 +4315,7 @@
         <v>2066.8205921498902</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>2018</v>
       </c>
@@ -4311,7 +4323,7 @@
         <v>2546.32296952867</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>2019</v>
       </c>
@@ -4319,7 +4331,7 @@
         <v>3860.2256218054599</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>2020</v>
       </c>
@@ -4327,7 +4339,7 @@
         <v>5921.5861038495796</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>2021</v>
       </c>
@@ -4347,13 +4359,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>36</v>
       </c>
@@ -4361,7 +4374,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>37</v>
       </c>
@@ -4369,7 +4382,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>38</v>
       </c>
@@ -4378,12 +4391,12 @@
         <v>26.136104337887964</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -4392,12 +4405,12 @@
         <v>1.0815815171318504</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>42</v>
       </c>
@@ -4405,19 +4418,19 @@
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
@@ -4437,25 +4450,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="21"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="22"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="24"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
@@ -4463,7 +4476,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>1969</v>
       </c>
@@ -4471,7 +4484,7 @@
         <v>152643.77335610599</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>1970</v>
       </c>
@@ -4479,7 +4492,7 @@
         <v>160860.95636173099</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>1971</v>
       </c>
@@ -4487,7 +4500,7 @@
         <v>166912.606221553</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>1972</v>
       </c>
@@ -4495,7 +4508,7 @@
         <v>170379.33445085399</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>1973</v>
       </c>
@@ -4503,7 +4516,7 @@
         <v>176760.97430606201</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>1974</v>
       </c>
@@ -4511,7 +4524,7 @@
         <v>186316.01795022801</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>1975</v>
       </c>
@@ -4519,7 +4532,7 @@
         <v>185210.551465686</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>1976</v>
       </c>
@@ -4527,7 +4540,7 @@
         <v>185188.55213266</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>1977</v>
       </c>
@@ -4535,7 +4548,7 @@
         <v>197015.02691173099</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>1978</v>
       </c>
@@ -4543,7 +4556,7 @@
         <v>190666.38605606201</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>1979</v>
       </c>
@@ -4551,7 +4564,7 @@
         <v>203891.651760017</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>1980</v>
       </c>
@@ -4559,7 +4572,7 @@
         <v>207011.43217472499</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>1981</v>
       </c>
@@ -4567,7 +4580,7 @@
         <v>195787.085571267</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>1982</v>
       </c>
@@ -4575,7 +4588,7 @@
         <v>189602.24152446401</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>1983</v>
       </c>
@@ -4583,7 +4596,7 @@
         <v>197400.610512652</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>1984</v>
       </c>
@@ -4591,7 +4604,7 @@
         <v>201349.024597112</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>1985</v>
       </c>
@@ -4599,7 +4612,7 @@
         <v>187351.74596487399</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>1986</v>
       </c>
@@ -4607,7 +4620,7 @@
         <v>200726.11957615399</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>1987</v>
       </c>
@@ -4615,7 +4628,7 @@
         <v>205926.37181563699</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>1988</v>
       </c>
@@ -4623,7 +4636,7 @@
         <v>202022.16389395401</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>1989</v>
       </c>
@@ -4631,7 +4644,7 @@
         <v>188010.819664468</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>1990</v>
       </c>
@@ -4639,7 +4652,7 @@
         <v>184568.767080916</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>1991</v>
       </c>
@@ -4647,7 +4660,7 @@
         <v>204093.82543139899</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>1992</v>
       </c>
@@ -4655,7 +4668,7 @@
         <v>223701.26799433099</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>1993</v>
       </c>
@@ -4663,7 +4676,7 @@
         <v>236504.98023157299</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>1994</v>
       </c>
@@ -4671,7 +4684,7 @@
         <v>250307.88553631501</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>1995</v>
       </c>
@@ -4679,7 +4692,7 @@
         <v>243186.10151946</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>1996</v>
       </c>
@@ -4687,7 +4700,7 @@
         <v>256626.24305584701</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>1997</v>
       </c>
@@ -4695,7 +4708,7 @@
         <v>277441.31762237998</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>1998</v>
       </c>
@@ -4703,7 +4716,7 @@
         <v>288122.80460772401</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>1999</v>
       </c>
@@ -4711,7 +4724,7 @@
         <v>278369.01387171802</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>2000</v>
       </c>
@@ -4719,7 +4732,7 @@
         <v>276172.18535265001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>2001</v>
       </c>
@@ -4727,7 +4740,7 @@
         <v>263995.67436681699</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>2002</v>
       </c>
@@ -4735,7 +4748,7 @@
         <v>235234.596752907</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>2003</v>
       </c>
@@ -4743,7 +4756,7 @@
         <v>256022.46524751</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>2004</v>
       </c>
@@ -4764,13 +4777,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>45</v>
       </c>
@@ -4778,7 +4791,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>60</v>
       </c>
@@ -4786,7 +4799,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>46</v>
       </c>
@@ -4795,7 +4808,7 @@
         <v>7.1386437005970027E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
@@ -4804,12 +4817,12 @@
         <v>649.43174288959028</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>48</v>
       </c>
@@ -4817,13 +4830,13 @@
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -4843,15 +4856,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="4" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>49</v>
       </c>
@@ -4859,7 +4872,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>59</v>
       </c>
@@ -4867,7 +4880,7 @@
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>21</v>
       </c>
@@ -4881,7 +4894,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>1970</v>
       </c>
@@ -4894,7 +4907,7 @@
       </c>
       <c r="D5" s="12"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>1971</v>
       </c>
@@ -4910,7 +4923,7 @@
         <v>6.6936796094821949E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>1972</v>
       </c>
@@ -4926,7 +4939,7 @@
         <v>6.5338955174785163E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>1973</v>
       </c>
@@ -4942,7 +4955,7 @@
         <v>2.2651995733453223E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>1974</v>
       </c>
@@ -4958,7 +4971,7 @@
         <v>0.11538989377761943</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>1975</v>
       </c>
@@ -4974,7 +4987,7 @@
         <v>-0.12591972832640219</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>1976</v>
       </c>
@@ -4990,7 +5003,7 @@
         <v>0.13752815315315314</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>1977</v>
       </c>
@@ -5006,7 +5019,7 @@
         <v>-5.7963123375819881E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>1978</v>
       </c>
@@ -5022,7 +5035,7 @@
         <v>0.11289178467277927</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>1979</v>
       </c>
@@ -5038,7 +5051,7 @@
         <v>0.13562322946175653</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>1980</v>
       </c>
@@ -5054,7 +5067,7 @@
         <v>-0.10770190208917985</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>1981</v>
       </c>
@@ -5070,7 +5083,7 @@
         <v>-0.18034199981362431</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>1982</v>
       </c>
@@ -5086,7 +5099,7 @@
         <v>2.4443623340818288E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>1983</v>
       </c>
@@ -5102,7 +5115,7 @@
         <v>0.16322170740504371</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>1984</v>
       </c>
@@ -5118,7 +5131,7 @@
         <v>-3.5347994084815926E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>1985</v>
       </c>
@@ -5134,7 +5147,7 @@
         <v>-4.9030758579764688E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>1986</v>
       </c>
@@ -5150,7 +5163,7 @@
         <v>7.1386437005970027E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>1987</v>
       </c>
@@ -5166,7 +5179,7 @@
         <v>1.2866920993226394E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>1988</v>
       </c>
@@ -5182,7 +5195,7 @@
         <v>-2.4272095391290383E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>1989</v>
       </c>
@@ -5198,7 +5211,7 @@
         <v>-4.1830356974057792E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>1990</v>
       </c>
@@ -5214,7 +5227,7 @@
         <v>8.5631979795586233E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>1991</v>
       </c>
@@ -5230,7 +5243,7 @@
         <v>-2.1619949021637663E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>1992</v>
       </c>
@@ -5246,7 +5259,7 @@
         <v>8.4730252294494379E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>1993</v>
       </c>
@@ -5262,7 +5275,7 @@
         <v>0.10326652390160662</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>1994</v>
       </c>
@@ -5278,7 +5291,7 @@
         <v>4.3357563520997067E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="11">
         <v>1995</v>
       </c>
@@ -5294,7 +5307,7 @@
         <v>-2.336580185560666E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="11">
         <v>1996</v>
       </c>
@@ -5310,7 +5323,7 @@
         <v>2.8645327411909172E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>1997</v>
       </c>
@@ -5326,7 +5339,7 @@
         <v>9.4721977867370466E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>1998</v>
       </c>
@@ -5342,7 +5355,7 @@
         <v>6.5387282637103139E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>1999</v>
       </c>
@@ -5358,7 +5371,7 @@
         <v>-2.4839103312047861E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>2000</v>
       </c>
@@ -5374,7 +5387,7 @@
         <v>-2.7081718351090411E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>2001</v>
       </c>
@@ -5390,7 +5403,7 @@
         <v>-7.5432354387124145E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="11">
         <v>2002</v>
       </c>
@@ -5406,7 +5419,7 @@
         <v>-6.6177566696846712E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <v>2003</v>
       </c>
@@ -5422,7 +5435,7 @@
         <v>0.20171019152567249</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="11">
         <v>2004</v>
       </c>
@@ -5438,7 +5451,7 @@
         <v>0.16434808068002815</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>2005</v>
       </c>
@@ -5454,7 +5467,7 @@
         <v>4.6513803403071208E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <v>2006</v>
       </c>
@@ -5470,7 +5483,7 @@
         <v>7.7195222681360143E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="11">
         <v>2007</v>
       </c>
@@ -5486,7 +5499,7 @@
         <v>4.1716449950309986E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="11">
         <v>2008</v>
       </c>
@@ -5502,7 +5515,7 @@
         <v>2.3057070180426908E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>2009</v>
       </c>
@@ -5518,7 +5531,7 @@
         <v>-2.7891879130777397E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="11">
         <v>2010</v>
       </c>
@@ -5534,7 +5547,7 @@
         <v>4.4223332102990343E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
         <v>2011</v>
       </c>
@@ -5550,7 +5563,7 @@
         <v>3.5977714375441838E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="11">
         <v>2012</v>
       </c>
@@ -5566,7 +5579,7 @@
         <v>-1.4156037666630872E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <v>2013</v>
       </c>
@@ -5582,7 +5595,7 @@
         <v>4.9200721123227709E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="11">
         <v>2014</v>
       </c>
@@ -5598,7 +5611,7 @@
         <v>-3.6842630268091425E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
         <v>2015</v>
       </c>
@@ -5614,7 +5627,7 @@
         <v>3.6643876408434695E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="11">
         <v>2016</v>
       </c>
@@ -5630,7 +5643,7 @@
         <v>-5.754253235777973E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="11">
         <v>2017</v>
       </c>
@@ -5646,7 +5659,7 @@
         <v>2.1123875796110525E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="11">
         <v>2018</v>
       </c>
@@ -5662,7 +5675,7 @@
         <v>-5.1177207495317623E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="11">
         <v>2019</v>
       </c>
@@ -5678,7 +5691,7 @@
         <v>-1.2863316386648838E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="11">
         <v>2020</v>
       </c>
@@ -5694,7 +5707,7 @@
         <v>-7.9652330003202265E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11">
         <v>2021</v>
       </c>
@@ -5710,7 +5723,7 @@
         <v>0.1047783253631982</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="17">
         <v>2022</v>
       </c>
